--- a/data/CONTROL_DE_VIVENCIA.xlsx
+++ b/data/CONTROL_DE_VIVENCIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jronquilla\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B39058-50A2-4B66-B340-F63351D1574E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0445A1-4BF1-45E3-90E3-FECCE7B4CEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8321" uniqueCount="1470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8351" uniqueCount="1477">
   <si>
     <t>ABIGAIL  MEJIA CHOQUECALLATA VDA.DE MUÑOZ</t>
   </si>
@@ -4446,7 +4446,28 @@
     <t>PRESENTAR</t>
   </si>
   <si>
-    <t>CERTIFICADO DE ESTUDIO HASTA EL 15/02/2027</t>
+    <t>CERTIFICADO DE ESTUDIO 15/12/2025</t>
+  </si>
+  <si>
+    <t>CERTIFICADO DE ESTUDIO 15/11/2026</t>
+  </si>
+  <si>
+    <t>CERTIFICADO DE ESTUDIO 15/02/2027</t>
+  </si>
+  <si>
+    <t>CERTIFICADO DE ESTUDIO 15/03/2025</t>
+  </si>
+  <si>
+    <t>CERTIFICADO DE ESTUDIO 15/01/2027</t>
+  </si>
+  <si>
+    <t>CERTIFICADO DE ESTUDIO 15/03/2027</t>
+  </si>
+  <si>
+    <t>CERTIFICADO DE ESTUDIO 15/08/2026</t>
+  </si>
+  <si>
+    <t>CERTIFICADO DE ESTUDIO 15/12/2026</t>
   </si>
 </sst>
 </file>
@@ -4512,7 +4533,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -4586,11 +4607,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4640,6 +4676,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4663,7 +4704,7 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -4672,8 +4713,6 @@
           <color indexed="64"/>
         </top>
         <bottom/>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -4693,7 +4732,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -4702,8 +4741,6 @@
           <color indexed="64"/>
         </top>
         <bottom/>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -5270,13 +5307,13 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="58.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" customWidth="1"/>
+    <col min="3" max="3" width="57.88671875" customWidth="1"/>
+    <col min="4" max="4" width="58.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.21875" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" customWidth="1"/>
+    <col min="7" max="7" width="33.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="42" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -10893,7 +10930,9 @@
       <c r="G234" s="12" t="s">
         <v>1461</v>
       </c>
-      <c r="H234" s="17"/>
+      <c r="H234" s="19" t="s">
+        <v>1473</v>
+      </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" s="8">
@@ -10989,7 +11028,9 @@
       <c r="G238" s="11" t="s">
         <v>1461</v>
       </c>
-      <c r="H238" s="17"/>
+      <c r="H238" s="19" t="s">
+        <v>1470</v>
+      </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" s="8">
@@ -11133,7 +11174,9 @@
       <c r="G244" s="12" t="s">
         <v>1461</v>
       </c>
-      <c r="H244" s="17"/>
+      <c r="H244" s="19" t="s">
+        <v>1474</v>
+      </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" s="9">
@@ -11157,7 +11200,9 @@
       <c r="G245" s="12" t="s">
         <v>1461</v>
       </c>
-      <c r="H245" s="17"/>
+      <c r="H245" s="19" t="s">
+        <v>1474</v>
+      </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" s="8">
@@ -11229,7 +11274,9 @@
       <c r="G248" s="11" t="s">
         <v>1461</v>
       </c>
-      <c r="H248" s="17"/>
+      <c r="H248" s="19" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" s="8">
@@ -11325,7 +11372,9 @@
       <c r="G252" s="12" t="s">
         <v>1461</v>
       </c>
-      <c r="H252" s="17"/>
+      <c r="H252" s="19" t="s">
+        <v>1474</v>
+      </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" s="9">
@@ -11373,7 +11422,9 @@
       <c r="G254" s="11" t="s">
         <v>1461</v>
       </c>
-      <c r="H254" s="17"/>
+      <c r="H254" s="19" t="s">
+        <v>1474</v>
+      </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" s="9">
@@ -11445,7 +11496,9 @@
       <c r="G257" s="11" t="s">
         <v>1461</v>
       </c>
-      <c r="H257" s="17"/>
+      <c r="H257" s="19" t="s">
+        <v>1474</v>
+      </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" s="9">
@@ -11469,7 +11522,9 @@
       <c r="G258" s="12" t="s">
         <v>1461</v>
       </c>
-      <c r="H258" s="17"/>
+      <c r="H258" s="19" t="s">
+        <v>1474</v>
+      </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" s="8">
@@ -11493,7 +11548,9 @@
       <c r="G259" s="11" t="s">
         <v>1461</v>
       </c>
-      <c r="H259" s="17"/>
+      <c r="H259" s="19" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" s="9" t="s">
@@ -24345,8 +24402,8 @@
       <c r="G795" s="11" t="s">
         <v>1462</v>
       </c>
-      <c r="H795" s="17" t="s">
-        <v>1469</v>
+      <c r="H795" s="21" t="s">
+        <v>1471</v>
       </c>
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.3">
@@ -24683,7 +24740,9 @@
       <c r="G809" s="12" t="s">
         <v>1462</v>
       </c>
-      <c r="H809" s="17"/>
+      <c r="H809" s="19" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="810" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A810" s="8">
@@ -24731,7 +24790,9 @@
       <c r="G811" s="11" t="s">
         <v>1462</v>
       </c>
-      <c r="H811" s="17"/>
+      <c r="H811" s="19" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="812" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A812" s="9">
@@ -24827,7 +24888,9 @@
       <c r="G815" s="12" t="s">
         <v>1462</v>
       </c>
-      <c r="H815" s="17"/>
+      <c r="H815" s="19" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="816" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A816" s="9">
@@ -24899,7 +24962,9 @@
       <c r="G818" s="11" t="s">
         <v>1462</v>
       </c>
-      <c r="H818" s="17"/>
+      <c r="H818" s="19" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="819" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A819" s="9">
@@ -24923,7 +24988,9 @@
       <c r="G819" s="12" t="s">
         <v>1462</v>
       </c>
-      <c r="H819" s="17"/>
+      <c r="H819" s="19" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="820" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A820" s="8">
@@ -24971,7 +25038,9 @@
       <c r="G821" s="11" t="s">
         <v>1462</v>
       </c>
-      <c r="H821" s="17"/>
+      <c r="H821" s="19" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="822" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A822" s="8">
@@ -25113,7 +25182,9 @@
       <c r="G827" s="12" t="s">
         <v>1462</v>
       </c>
-      <c r="H827" s="17"/>
+      <c r="H827" s="19" t="s">
+        <v>1473</v>
+      </c>
     </row>
     <row r="828" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A828" s="9">
@@ -25161,7 +25232,9 @@
       <c r="G829" s="12" t="s">
         <v>1462</v>
       </c>
-      <c r="H829" s="17"/>
+      <c r="H829" s="19" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="830" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A830" s="8">
@@ -25231,7 +25304,9 @@
       <c r="G832" s="11" t="s">
         <v>1462</v>
       </c>
-      <c r="H832" s="17"/>
+      <c r="H832" s="19" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="833" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A833" s="8">
@@ -25303,7 +25378,9 @@
       <c r="G835" s="11" t="s">
         <v>1462</v>
       </c>
-      <c r="H835" s="17"/>
+      <c r="H835" s="19" t="s">
+        <v>1473</v>
+      </c>
     </row>
     <row r="836" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A836" s="9">
@@ -27821,7 +27898,9 @@
       <c r="G940" s="11" t="s">
         <v>1461</v>
       </c>
-      <c r="H940" s="17"/>
+      <c r="H940" s="19" t="s">
+        <v>1473</v>
+      </c>
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A941" s="9">
@@ -27917,7 +27996,9 @@
       <c r="G944" s="12" t="s">
         <v>1461</v>
       </c>
-      <c r="H944" s="17"/>
+      <c r="H944" s="19" t="s">
+        <v>1476</v>
+      </c>
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A945" s="8">
@@ -27989,7 +28070,9 @@
       <c r="G947" s="11" t="s">
         <v>1461</v>
       </c>
-      <c r="H947" s="17"/>
+      <c r="H947" s="19" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="948" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A948" s="8">
@@ -29357,7 +29440,9 @@
       <c r="G1004" s="12" t="s">
         <v>1461</v>
       </c>
-      <c r="H1004" s="17"/>
+      <c r="H1004" s="20" t="s">
+        <v>1472</v>
+      </c>
     </row>
     <row r="1005" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1005" s="8">
@@ -34853,7 +34938,9 @@
       <c r="G1233" s="12" t="s">
         <v>1463</v>
       </c>
-      <c r="H1233" s="17"/>
+      <c r="H1233" s="19" t="s">
+        <v>1469</v>
+      </c>
     </row>
     <row r="1234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1234" s="8">
@@ -34973,7 +35060,9 @@
       <c r="G1238" s="11" t="s">
         <v>1463</v>
       </c>
-      <c r="H1238" s="17"/>
+      <c r="H1238" s="19" t="s">
+        <v>1475</v>
+      </c>
     </row>
     <row r="1239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1239" s="8">
@@ -35237,7 +35326,9 @@
       <c r="G1249" s="12" t="s">
         <v>1463</v>
       </c>
-      <c r="H1249" s="17"/>
+      <c r="H1249" s="19" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="1250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1250" s="9">
@@ -35333,7 +35424,9 @@
       <c r="G1253" s="11" t="s">
         <v>1463</v>
       </c>
-      <c r="H1253" s="17"/>
+      <c r="H1253" s="19" t="s">
+        <v>1474</v>
+      </c>
     </row>
     <row r="1254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1254" s="9">
@@ -35405,7 +35498,9 @@
       <c r="G1256" s="12" t="s">
         <v>1463</v>
       </c>
-      <c r="H1256" s="17"/>
+      <c r="H1256" s="19" t="s">
+        <v>1470</v>
+      </c>
     </row>
     <row r="1257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1257" s="8">
@@ -38045,7 +38140,9 @@
       <c r="G1366" s="12" t="s">
         <v>1461</v>
       </c>
-      <c r="H1366" s="17"/>
+      <c r="H1366" s="19" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1367" s="9">
